--- a/artfynd/A 37406-2025 artfynd.xlsx
+++ b/artfynd/A 37406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589835</v>
+        <v>121589821</v>
       </c>
       <c r="B2" t="n">
-        <v>97085</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651023</v>
+        <v>650607</v>
       </c>
       <c r="R2" t="n">
-        <v>7170755</v>
+        <v>7170753</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589858</v>
+        <v>121589828</v>
       </c>
       <c r="B3" t="n">
-        <v>98131</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,26 +787,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650846</v>
+        <v>650645</v>
       </c>
       <c r="R3" t="n">
-        <v>7170647</v>
+        <v>7170985</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,42 +877,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589861</v>
+        <v>121589857</v>
       </c>
       <c r="B4" t="n">
-        <v>98131</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650816</v>
+        <v>650826</v>
       </c>
       <c r="R4" t="n">
-        <v>7170626</v>
+        <v>7170658</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,7 +956,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera blommar</t>
+          <t>Flera fruktkroppar på stående död gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589843</v>
+        <v>121589859</v>
       </c>
       <c r="B5" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,21 +994,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651069</v>
+        <v>650836</v>
       </c>
       <c r="R5" t="n">
-        <v>7170647</v>
+        <v>7170651</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,37 +1084,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589853</v>
+        <v>121589832</v>
       </c>
       <c r="B6" t="n">
-        <v>79746</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>1588</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1148,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650880</v>
+        <v>650886</v>
       </c>
       <c r="R6" t="n">
-        <v>7170682</v>
+        <v>7170833</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589832</v>
+        <v>121589844</v>
       </c>
       <c r="B7" t="n">
-        <v>90908</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650886</v>
+        <v>651065</v>
       </c>
       <c r="R7" t="n">
-        <v>7170833</v>
+        <v>7170686</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,15 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589855</v>
+        <v>121589841</v>
       </c>
       <c r="B8" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1297,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1360,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650892</v>
+        <v>651098</v>
       </c>
       <c r="R8" t="n">
-        <v>7170693</v>
+        <v>7170643</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1396,11 +1361,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer pa grov sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,37 +1387,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589859</v>
+        <v>121589829</v>
       </c>
       <c r="B9" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1471,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650836</v>
+        <v>650789</v>
       </c>
       <c r="R9" t="n">
-        <v>7170651</v>
+        <v>7170866</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1533,15 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589860</v>
+        <v>121589830</v>
       </c>
       <c r="B10" t="n">
-        <v>98131</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,26 +1499,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1577,10 +1527,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650830</v>
+        <v>650815</v>
       </c>
       <c r="R10" t="n">
-        <v>7170622</v>
+        <v>7170874</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1639,19 +1589,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589862</v>
+        <v>121589834</v>
       </c>
       <c r="B11" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1683,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650799</v>
+        <v>650935</v>
       </c>
       <c r="R11" t="n">
-        <v>7170628</v>
+        <v>7170775</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1745,37 +1690,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589836</v>
+        <v>121589837</v>
       </c>
       <c r="B12" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651064</v>
+        <v>651072</v>
       </c>
       <c r="R12" t="n">
-        <v>7170712</v>
+        <v>7170724</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1851,32 +1791,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589819</v>
+        <v>121589842</v>
       </c>
       <c r="B13" t="n">
-        <v>79745</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1895,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650739</v>
+        <v>651053</v>
       </c>
       <c r="R13" t="n">
-        <v>7170646</v>
+        <v>7170636</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1957,19 +1892,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589842</v>
+        <v>121589862</v>
       </c>
       <c r="B14" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2001,10 +1931,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651053</v>
+        <v>650799</v>
       </c>
       <c r="R14" t="n">
-        <v>7170636</v>
+        <v>7170628</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2063,15 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589833</v>
+        <v>121589863</v>
       </c>
       <c r="B15" t="n">
-        <v>98131</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2079,26 +2004,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2107,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650931</v>
+        <v>650786</v>
       </c>
       <c r="R15" t="n">
-        <v>7170785</v>
+        <v>7170620</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2169,15 +2094,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589830</v>
+        <v>121589820</v>
       </c>
       <c r="B16" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,21 +2105,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2213,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650815</v>
+        <v>650739</v>
       </c>
       <c r="R16" t="n">
-        <v>7170874</v>
+        <v>7170646</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2275,37 +2195,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589847</v>
+        <v>121589839</v>
       </c>
       <c r="B17" t="n">
-        <v>79745</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2319,10 +2234,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651045</v>
+        <v>651123</v>
       </c>
       <c r="R17" t="n">
-        <v>7170684</v>
+        <v>7170655</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2381,15 +2296,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589850</v>
+        <v>121589843</v>
       </c>
       <c r="B18" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2425,10 +2335,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651040</v>
+        <v>651069</v>
       </c>
       <c r="R18" t="n">
-        <v>7170694</v>
+        <v>7170647</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2487,15 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589831</v>
+        <v>121589846</v>
       </c>
       <c r="B19" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,21 +2408,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2531,10 +2436,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650882</v>
+        <v>651020</v>
       </c>
       <c r="R19" t="n">
-        <v>7170828</v>
+        <v>7170657</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2567,6 +2472,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,15 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589857</v>
+        <v>121589848</v>
       </c>
       <c r="B20" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,21 +2514,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2637,10 +2542,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650826</v>
+        <v>651044</v>
       </c>
       <c r="R20" t="n">
-        <v>7170658</v>
+        <v>7170685</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2673,11 +2578,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar på stående död gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,37 +2604,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589849</v>
+        <v>121589850</v>
       </c>
       <c r="B21" t="n">
-        <v>79739</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2748,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651041</v>
+        <v>651040</v>
       </c>
       <c r="R21" t="n">
-        <v>7170695</v>
+        <v>7170694</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2810,15 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589841</v>
+        <v>121589851</v>
       </c>
       <c r="B22" t="n">
-        <v>79711</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2716,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2854,10 +2744,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651098</v>
+        <v>650992</v>
       </c>
       <c r="R22" t="n">
-        <v>7170643</v>
+        <v>7170679</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2916,15 +2806,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589851</v>
+        <v>121589855</v>
       </c>
       <c r="B23" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2960,10 +2845,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>650992</v>
+        <v>650892</v>
       </c>
       <c r="R23" t="n">
-        <v>7170679</v>
+        <v>7170693</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2996,6 +2881,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Växer pa grov sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,15 +2912,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589829</v>
+        <v>121589865</v>
       </c>
       <c r="B24" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3038,21 +2923,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3066,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>650789</v>
+        <v>650742</v>
       </c>
       <c r="R24" t="n">
-        <v>7170866</v>
+        <v>7170597</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3102,6 +2987,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,37 +3018,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121589834</v>
+        <v>121589838</v>
       </c>
       <c r="B25" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3172,10 +3057,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>650935</v>
+        <v>651123</v>
       </c>
       <c r="R25" t="n">
-        <v>7170775</v>
+        <v>7170655</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3234,15 +3119,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121589854</v>
+        <v>121589849</v>
       </c>
       <c r="B26" t="n">
-        <v>79739</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3278,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>650895</v>
+        <v>651041</v>
       </c>
       <c r="R26" t="n">
-        <v>7170701</v>
+        <v>7170695</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3340,37 +3220,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121589839</v>
+        <v>121589854</v>
       </c>
       <c r="B27" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3384,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>651123</v>
+        <v>650895</v>
       </c>
       <c r="R27" t="n">
-        <v>7170655</v>
+        <v>7170701</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3446,32 +3321,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121589837</v>
+        <v>121589819</v>
       </c>
       <c r="B28" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3490,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651072</v>
+        <v>650739</v>
       </c>
       <c r="R28" t="n">
-        <v>7170724</v>
+        <v>7170646</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3552,37 +3422,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121589820</v>
+        <v>121589847</v>
       </c>
       <c r="B29" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3596,10 +3461,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>650739</v>
+        <v>651045</v>
       </c>
       <c r="R29" t="n">
-        <v>7170646</v>
+        <v>7170684</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3658,15 +3523,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121589864</v>
+        <v>121589845</v>
       </c>
       <c r="B30" t="n">
-        <v>79746</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3702,10 +3562,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>650742</v>
+        <v>651040</v>
       </c>
       <c r="R30" t="n">
-        <v>7170597</v>
+        <v>7170672</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3738,6 +3598,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3764,37 +3629,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121589840</v>
+        <v>121589853</v>
       </c>
       <c r="B31" t="n">
-        <v>57518</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3802,24 +3662,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651113</v>
+        <v>650880</v>
       </c>
       <c r="R31" t="n">
-        <v>7170655</v>
+        <v>7170682</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3852,11 +3704,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3883,42 +3730,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121589817</v>
+        <v>121589864</v>
       </c>
       <c r="B32" t="n">
-        <v>98131</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3927,10 +3769,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>650754</v>
+        <v>650742</v>
       </c>
       <c r="R32" t="n">
-        <v>7170637</v>
+        <v>7170597</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3989,37 +3831,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121589856</v>
+        <v>121589840</v>
       </c>
       <c r="B33" t="n">
-        <v>98048</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4027,16 +3864,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>650844</v>
+        <v>651113</v>
       </c>
       <c r="R33" t="n">
-        <v>7170673</v>
+        <v>7170655</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4069,6 +3914,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4095,15 +3945,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121589838</v>
+        <v>121589856</v>
       </c>
       <c r="B34" t="n">
-        <v>79739</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4111,21 +3956,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4139,10 +3984,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651123</v>
+        <v>650844</v>
       </c>
       <c r="R34" t="n">
-        <v>7170655</v>
+        <v>7170673</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4201,42 +4046,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121589863</v>
+        <v>121589817</v>
       </c>
       <c r="B35" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4245,10 +4085,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>650786</v>
+        <v>650754</v>
       </c>
       <c r="R35" t="n">
-        <v>7170620</v>
+        <v>7170637</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4307,42 +4147,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121589865</v>
+        <v>121589818</v>
       </c>
       <c r="B36" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4351,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>650742</v>
+        <v>650745</v>
       </c>
       <c r="R36" t="n">
-        <v>7170597</v>
+        <v>7170644</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4387,11 +4222,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Växer på grov flerstammig sälg</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4418,42 +4248,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121589848</v>
+        <v>121589833</v>
       </c>
       <c r="B37" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4462,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651044</v>
+        <v>650931</v>
       </c>
       <c r="R37" t="n">
-        <v>7170685</v>
+        <v>7170785</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4524,42 +4349,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121589828</v>
+        <v>121589852</v>
       </c>
       <c r="B38" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4568,10 +4388,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>650645</v>
+        <v>650913</v>
       </c>
       <c r="R38" t="n">
-        <v>7170985</v>
+        <v>7170668</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4630,42 +4450,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121589846</v>
+        <v>121589858</v>
       </c>
       <c r="B39" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4674,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651020</v>
+        <v>650846</v>
       </c>
       <c r="R39" t="n">
-        <v>7170657</v>
+        <v>7170647</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4710,11 +4525,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Växer på rönn</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,15 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121589852</v>
+        <v>121589860</v>
       </c>
       <c r="B40" t="n">
-        <v>98131</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4776,7 +4581,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4785,10 +4590,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>650913</v>
+        <v>650830</v>
       </c>
       <c r="R40" t="n">
-        <v>7170668</v>
+        <v>7170622</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4847,42 +4652,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121589844</v>
+        <v>121589861</v>
       </c>
       <c r="B41" t="n">
-        <v>90908</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4891,10 +4691,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651065</v>
+        <v>650816</v>
       </c>
       <c r="R41" t="n">
-        <v>7170686</v>
+        <v>7170626</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4927,6 +4727,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Flera blommar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4953,42 +4758,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121589818</v>
+        <v>121589835</v>
       </c>
       <c r="B42" t="n">
-        <v>98131</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4997,10 +4797,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>650745</v>
+        <v>651023</v>
       </c>
       <c r="R42" t="n">
-        <v>7170644</v>
+        <v>7170755</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5056,117 +4856,6 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>121589845</v>
-      </c>
-      <c r="B43" t="n">
-        <v>79746</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Fäboliden, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>651040</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7170672</v>
-      </c>
-      <c r="S43" t="n">
-        <v>5</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Växer på rönn</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37406-2025 artfynd.xlsx
+++ b/artfynd/A 37406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589857</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589859</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589832</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589844</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589841</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589821</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589828</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589829</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589830</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589834</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589837</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589842</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589862</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589863</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589820</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2293,6 +2373,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589839</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2394,6 +2479,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589843</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2500,6 +2590,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589846</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2601,6 +2696,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589848</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2702,6 +2802,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589850</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2803,6 +2908,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589851</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2909,6 +3019,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589855</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3015,6 +3130,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589865</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3116,6 +3236,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589838</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3217,6 +3342,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589849</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3318,6 +3448,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589854</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3419,6 +3554,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589819</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3520,6 +3660,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589847</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3626,6 +3771,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589845</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3727,6 +3877,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589853</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3828,6 +3983,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589864</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3942,6 +4102,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589840</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4043,6 +4208,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589856</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4144,6 +4314,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589817</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4245,6 +4420,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589818</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4346,6 +4526,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589833</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4447,6 +4632,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589852</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4548,6 +4738,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589858</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4649,6 +4844,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589860</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4755,6 +4955,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589861</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4856,8 +5061,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589835</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>